--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q734"/>
+  <dimension ref="A1:Q736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29339,6 +29339,92 @@
       <c r="P734" t="inlineStr"/>
       <c r="Q734" t="inlineStr"/>
     </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B735" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C735" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D735" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E735" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F735" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G735" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H735" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I735" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J735" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K735" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L735" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M735" t="inlineStr"/>
+      <c r="N735" t="inlineStr"/>
+      <c r="O735" t="inlineStr"/>
+      <c r="P735" t="inlineStr"/>
+      <c r="Q735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B736" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C736" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D736" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E736" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F736" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G736" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H736" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I736" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J736" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K736" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L736" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" t="inlineStr"/>
+      <c r="O736" t="inlineStr"/>
+      <c r="P736" t="inlineStr"/>
+      <c r="Q736" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q736"/>
+  <dimension ref="A1:Q737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29425,6 +29425,49 @@
       <c r="P736" t="inlineStr"/>
       <c r="Q736" t="inlineStr"/>
     </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B737" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C737" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D737" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E737" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F737" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G737" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H737" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I737" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J737" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K737" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L737" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" t="inlineStr"/>
+      <c r="O737" t="inlineStr"/>
+      <c r="P737" t="inlineStr"/>
+      <c r="Q737" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q737"/>
+  <dimension ref="A1:Q741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29468,6 +29468,178 @@
       <c r="P737" t="inlineStr"/>
       <c r="Q737" t="inlineStr"/>
     </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B738" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C738" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D738" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E738" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F738" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G738" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H738" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I738" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J738" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K738" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L738" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr"/>
+      <c r="O738" t="inlineStr"/>
+      <c r="P738" t="inlineStr"/>
+      <c r="Q738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B739" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C739" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D739" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E739" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F739" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G739" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H739" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I739" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J739" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K739" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L739" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr"/>
+      <c r="O739" t="inlineStr"/>
+      <c r="P739" t="inlineStr"/>
+      <c r="Q739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B740" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C740" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D740" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E740" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F740" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G740" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H740" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I740" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J740" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K740" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L740" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr"/>
+      <c r="O740" t="inlineStr"/>
+      <c r="P740" t="inlineStr"/>
+      <c r="Q740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B741" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C741" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D741" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E741" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G741" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H741" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I741" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J741" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K741" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L741" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr"/>
+      <c r="O741" t="inlineStr"/>
+      <c r="P741" t="inlineStr"/>
+      <c r="Q741" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q741"/>
+  <dimension ref="A1:Q743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29640,6 +29640,88 @@
       <c r="P741" t="inlineStr"/>
       <c r="Q741" t="inlineStr"/>
     </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B742" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C742" t="n">
+        <v>0.01989827</v>
+      </c>
+      <c r="D742" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E742" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0.22327515</v>
+      </c>
+      <c r="G742" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H742" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I742" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J742" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K742" t="inlineStr"/>
+      <c r="L742" t="n">
+        <v>0.02794965</v>
+      </c>
+      <c r="M742" t="inlineStr"/>
+      <c r="N742" t="inlineStr"/>
+      <c r="O742" t="inlineStr"/>
+      <c r="P742" t="inlineStr"/>
+      <c r="Q742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B743" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C743" t="n">
+        <v>0.01989827</v>
+      </c>
+      <c r="D743" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E743" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F743" t="n">
+        <v>0.22327515</v>
+      </c>
+      <c r="G743" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H743" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I743" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J743" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K743" t="inlineStr"/>
+      <c r="L743" t="n">
+        <v>0.02794965</v>
+      </c>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" t="inlineStr"/>
+      <c r="O743" t="inlineStr"/>
+      <c r="P743" t="inlineStr"/>
+      <c r="Q743" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q743"/>
+  <dimension ref="A1:Q744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29722,6 +29722,47 @@
       <c r="P743" t="inlineStr"/>
       <c r="Q743" t="inlineStr"/>
     </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B744" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C744" t="n">
+        <v>0.01989827</v>
+      </c>
+      <c r="D744" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E744" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F744" t="n">
+        <v>0.22327515</v>
+      </c>
+      <c r="G744" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H744" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I744" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J744" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K744" t="inlineStr"/>
+      <c r="L744" t="n">
+        <v>0.02794965</v>
+      </c>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" t="inlineStr"/>
+      <c r="O744" t="inlineStr"/>
+      <c r="P744" t="inlineStr"/>
+      <c r="Q744" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q744"/>
+  <dimension ref="A1:Q745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29763,6 +29763,49 @@
       <c r="P744" t="inlineStr"/>
       <c r="Q744" t="inlineStr"/>
     </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B745" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C745" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D745" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E745" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F745" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G745" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H745" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I745" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J745" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K745" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L745" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" t="inlineStr"/>
+      <c r="O745" t="inlineStr"/>
+      <c r="P745" t="inlineStr"/>
+      <c r="Q745" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q745"/>
+  <dimension ref="A1:Q746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29806,6 +29806,49 @@
       <c r="P745" t="inlineStr"/>
       <c r="Q745" t="inlineStr"/>
     </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B746" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C746" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D746" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E746" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H746" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I746" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J746" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K746" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L746" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M746" t="inlineStr"/>
+      <c r="N746" t="inlineStr"/>
+      <c r="O746" t="inlineStr"/>
+      <c r="P746" t="inlineStr"/>
+      <c r="Q746" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q746"/>
+  <dimension ref="A1:Q747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29849,6 +29849,49 @@
       <c r="P746" t="inlineStr"/>
       <c r="Q746" t="inlineStr"/>
     </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B747" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C747" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D747" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E747" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G747" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H747" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I747" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J747" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K747" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L747" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" t="inlineStr"/>
+      <c r="O747" t="inlineStr"/>
+      <c r="P747" t="inlineStr"/>
+      <c r="Q747" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q747"/>
+  <dimension ref="A1:Q749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29892,6 +29892,92 @@
       <c r="P747" t="inlineStr"/>
       <c r="Q747" t="inlineStr"/>
     </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B748" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C748" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D748" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E748" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G748" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H748" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I748" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J748" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K748" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L748" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M748" t="inlineStr"/>
+      <c r="N748" t="inlineStr"/>
+      <c r="O748" t="inlineStr"/>
+      <c r="P748" t="inlineStr"/>
+      <c r="Q748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B749" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C749" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D749" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E749" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F749" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G749" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H749" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I749" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J749" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K749" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L749" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M749" t="inlineStr"/>
+      <c r="N749" t="inlineStr"/>
+      <c r="O749" t="inlineStr"/>
+      <c r="P749" t="inlineStr"/>
+      <c r="Q749" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q749"/>
+  <dimension ref="A1:Q750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29978,6 +29978,49 @@
       <c r="P749" t="inlineStr"/>
       <c r="Q749" t="inlineStr"/>
     </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B750" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C750" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D750" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E750" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F750" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G750" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H750" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I750" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J750" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K750" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L750" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M750" t="inlineStr"/>
+      <c r="N750" t="inlineStr"/>
+      <c r="O750" t="inlineStr"/>
+      <c r="P750" t="inlineStr"/>
+      <c r="Q750" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q750"/>
+  <dimension ref="A1:Q751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30021,6 +30021,49 @@
       <c r="P750" t="inlineStr"/>
       <c r="Q750" t="inlineStr"/>
     </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B751" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C751" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D751" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E751" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F751" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G751" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H751" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I751" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J751" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K751" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L751" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" t="inlineStr"/>
+      <c r="O751" t="inlineStr"/>
+      <c r="P751" t="inlineStr"/>
+      <c r="Q751" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q751"/>
+  <dimension ref="A1:Q752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30064,6 +30064,49 @@
       <c r="P751" t="inlineStr"/>
       <c r="Q751" t="inlineStr"/>
     </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B752" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C752" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D752" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E752" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F752" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G752" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H752" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I752" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J752" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K752" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L752" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr"/>
+      <c r="O752" t="inlineStr"/>
+      <c r="P752" t="inlineStr"/>
+      <c r="Q752" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q752"/>
+  <dimension ref="A1:Q753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30107,6 +30107,49 @@
       <c r="P752" t="inlineStr"/>
       <c r="Q752" t="inlineStr"/>
     </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B753" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C753" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D753" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E753" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F753" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G753" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H753" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I753" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J753" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K753" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L753" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr"/>
+      <c r="O753" t="inlineStr"/>
+      <c r="P753" t="inlineStr"/>
+      <c r="Q753" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q753"/>
+  <dimension ref="A1:Q754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30150,6 +30150,49 @@
       <c r="P753" t="inlineStr"/>
       <c r="Q753" t="inlineStr"/>
     </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B754" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C754" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D754" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E754" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F754" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G754" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H754" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I754" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J754" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K754" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L754" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M754" t="inlineStr"/>
+      <c r="N754" t="inlineStr"/>
+      <c r="O754" t="inlineStr"/>
+      <c r="P754" t="inlineStr"/>
+      <c r="Q754" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q754"/>
+  <dimension ref="A1:Q755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30193,6 +30193,49 @@
       <c r="P754" t="inlineStr"/>
       <c r="Q754" t="inlineStr"/>
     </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B755" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C755" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D755" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E755" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F755" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G755" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H755" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I755" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J755" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K755" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L755" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M755" t="inlineStr"/>
+      <c r="N755" t="inlineStr"/>
+      <c r="O755" t="inlineStr"/>
+      <c r="P755" t="inlineStr"/>
+      <c r="Q755" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q756"/>
+  <dimension ref="A1:Q757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39084,21 +39084,11 @@
       <c r="L729" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M729" t="n">
-        <v>0</v>
-      </c>
-      <c r="N729" t="n">
-        <v>0</v>
-      </c>
-      <c r="O729" t="n">
-        <v>0</v>
-      </c>
-      <c r="P729" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q729" t="n">
-        <v>0</v>
-      </c>
+      <c r="M729" t="inlineStr"/>
+      <c r="N729" t="inlineStr"/>
+      <c r="O729" t="inlineStr"/>
+      <c r="P729" t="inlineStr"/>
+      <c r="Q729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
@@ -39137,21 +39127,11 @@
       <c r="L730" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M730" t="n">
-        <v>0</v>
-      </c>
-      <c r="N730" t="n">
-        <v>0</v>
-      </c>
-      <c r="O730" t="n">
-        <v>0</v>
-      </c>
-      <c r="P730" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q730" t="n">
-        <v>0</v>
-      </c>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" t="inlineStr"/>
+      <c r="O730" t="inlineStr"/>
+      <c r="P730" t="inlineStr"/>
+      <c r="Q730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
@@ -39190,21 +39170,11 @@
       <c r="L731" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M731" t="n">
-        <v>0</v>
-      </c>
-      <c r="N731" t="n">
-        <v>0</v>
-      </c>
-      <c r="O731" t="n">
-        <v>0</v>
-      </c>
-      <c r="P731" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q731" t="n">
-        <v>0</v>
-      </c>
+      <c r="M731" t="inlineStr"/>
+      <c r="N731" t="inlineStr"/>
+      <c r="O731" t="inlineStr"/>
+      <c r="P731" t="inlineStr"/>
+      <c r="Q731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
@@ -39243,21 +39213,11 @@
       <c r="L732" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M732" t="n">
-        <v>0</v>
-      </c>
-      <c r="N732" t="n">
-        <v>0</v>
-      </c>
-      <c r="O732" t="n">
-        <v>0</v>
-      </c>
-      <c r="P732" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q732" t="n">
-        <v>0</v>
-      </c>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" t="inlineStr"/>
+      <c r="O732" t="inlineStr"/>
+      <c r="P732" t="inlineStr"/>
+      <c r="Q732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
@@ -39296,21 +39256,11 @@
       <c r="L733" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M733" t="n">
-        <v>0</v>
-      </c>
-      <c r="N733" t="n">
-        <v>0</v>
-      </c>
-      <c r="O733" t="n">
-        <v>0</v>
-      </c>
-      <c r="P733" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q733" t="n">
-        <v>0</v>
-      </c>
+      <c r="M733" t="inlineStr"/>
+      <c r="N733" t="inlineStr"/>
+      <c r="O733" t="inlineStr"/>
+      <c r="P733" t="inlineStr"/>
+      <c r="Q733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
@@ -39349,21 +39299,11 @@
       <c r="L734" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M734" t="n">
-        <v>0</v>
-      </c>
-      <c r="N734" t="n">
-        <v>0</v>
-      </c>
-      <c r="O734" t="n">
-        <v>0</v>
-      </c>
-      <c r="P734" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q734" t="n">
-        <v>0</v>
-      </c>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" t="inlineStr"/>
+      <c r="O734" t="inlineStr"/>
+      <c r="P734" t="inlineStr"/>
+      <c r="Q734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
@@ -39402,21 +39342,11 @@
       <c r="L735" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M735" t="n">
-        <v>0</v>
-      </c>
-      <c r="N735" t="n">
-        <v>0</v>
-      </c>
-      <c r="O735" t="n">
-        <v>0</v>
-      </c>
-      <c r="P735" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q735" t="n">
-        <v>0</v>
-      </c>
+      <c r="M735" t="inlineStr"/>
+      <c r="N735" t="inlineStr"/>
+      <c r="O735" t="inlineStr"/>
+      <c r="P735" t="inlineStr"/>
+      <c r="Q735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
@@ -39561,21 +39491,11 @@
       <c r="L738" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M738" t="n">
-        <v>0</v>
-      </c>
-      <c r="N738" t="n">
-        <v>0</v>
-      </c>
-      <c r="O738" t="n">
-        <v>0</v>
-      </c>
-      <c r="P738" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q738" t="n">
-        <v>0</v>
-      </c>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr"/>
+      <c r="O738" t="inlineStr"/>
+      <c r="P738" t="inlineStr"/>
+      <c r="Q738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -39820,27 +39740,15 @@
       <c r="J743" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K743" t="n">
-        <v>0</v>
-      </c>
+      <c r="K743" t="inlineStr"/>
       <c r="L743" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M743" t="n">
-        <v>0</v>
-      </c>
-      <c r="N743" t="n">
-        <v>0</v>
-      </c>
-      <c r="O743" t="n">
-        <v>0</v>
-      </c>
-      <c r="P743" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q743" t="n">
-        <v>0</v>
-      </c>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" t="inlineStr"/>
+      <c r="O743" t="inlineStr"/>
+      <c r="P743" t="inlineStr"/>
+      <c r="Q743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
@@ -39873,27 +39781,15 @@
       <c r="J744" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K744" t="n">
-        <v>0</v>
-      </c>
+      <c r="K744" t="inlineStr"/>
       <c r="L744" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M744" t="n">
-        <v>0</v>
-      </c>
-      <c r="N744" t="n">
-        <v>0</v>
-      </c>
-      <c r="O744" t="n">
-        <v>0</v>
-      </c>
-      <c r="P744" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q744" t="n">
-        <v>0</v>
-      </c>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" t="inlineStr"/>
+      <c r="O744" t="inlineStr"/>
+      <c r="P744" t="inlineStr"/>
+      <c r="Q744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
@@ -40091,21 +39987,11 @@
       <c r="L748" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M748" t="n">
-        <v>0</v>
-      </c>
-      <c r="N748" t="n">
-        <v>0</v>
-      </c>
-      <c r="O748" t="n">
-        <v>0</v>
-      </c>
-      <c r="P748" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q748" t="n">
-        <v>0</v>
-      </c>
+      <c r="M748" t="inlineStr"/>
+      <c r="N748" t="inlineStr"/>
+      <c r="O748" t="inlineStr"/>
+      <c r="P748" t="inlineStr"/>
+      <c r="Q748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
@@ -40144,21 +40030,11 @@
       <c r="L749" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M749" t="n">
-        <v>0</v>
-      </c>
-      <c r="N749" t="n">
-        <v>0</v>
-      </c>
-      <c r="O749" t="n">
-        <v>0</v>
-      </c>
-      <c r="P749" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q749" t="n">
-        <v>0</v>
-      </c>
+      <c r="M749" t="inlineStr"/>
+      <c r="N749" t="inlineStr"/>
+      <c r="O749" t="inlineStr"/>
+      <c r="P749" t="inlineStr"/>
+      <c r="Q749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
@@ -40197,21 +40073,11 @@
       <c r="L750" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M750" t="n">
-        <v>0</v>
-      </c>
-      <c r="N750" t="n">
-        <v>0</v>
-      </c>
-      <c r="O750" t="n">
-        <v>0</v>
-      </c>
-      <c r="P750" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q750" t="n">
-        <v>0</v>
-      </c>
+      <c r="M750" t="inlineStr"/>
+      <c r="N750" t="inlineStr"/>
+      <c r="O750" t="inlineStr"/>
+      <c r="P750" t="inlineStr"/>
+      <c r="Q750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
@@ -40250,21 +40116,11 @@
       <c r="L751" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M751" t="n">
-        <v>0</v>
-      </c>
-      <c r="N751" t="n">
-        <v>0</v>
-      </c>
-      <c r="O751" t="n">
-        <v>0</v>
-      </c>
-      <c r="P751" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q751" t="n">
-        <v>0</v>
-      </c>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" t="inlineStr"/>
+      <c r="O751" t="inlineStr"/>
+      <c r="P751" t="inlineStr"/>
+      <c r="Q751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
@@ -40303,21 +40159,11 @@
       <c r="L752" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M752" t="n">
-        <v>0</v>
-      </c>
-      <c r="N752" t="n">
-        <v>0</v>
-      </c>
-      <c r="O752" t="n">
-        <v>0</v>
-      </c>
-      <c r="P752" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q752" t="n">
-        <v>0</v>
-      </c>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr"/>
+      <c r="O752" t="inlineStr"/>
+      <c r="P752" t="inlineStr"/>
+      <c r="Q752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
@@ -40356,21 +40202,11 @@
       <c r="L753" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M753" t="n">
-        <v>0</v>
-      </c>
-      <c r="N753" t="n">
-        <v>0</v>
-      </c>
-      <c r="O753" t="n">
-        <v>0</v>
-      </c>
-      <c r="P753" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q753" t="n">
-        <v>0</v>
-      </c>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr"/>
+      <c r="O753" t="inlineStr"/>
+      <c r="P753" t="inlineStr"/>
+      <c r="Q753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
@@ -40409,21 +40245,11 @@
       <c r="L754" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M754" t="n">
-        <v>0</v>
-      </c>
-      <c r="N754" t="n">
-        <v>0</v>
-      </c>
-      <c r="O754" t="n">
-        <v>0</v>
-      </c>
-      <c r="P754" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q754" t="n">
-        <v>0</v>
-      </c>
+      <c r="M754" t="inlineStr"/>
+      <c r="N754" t="inlineStr"/>
+      <c r="O754" t="inlineStr"/>
+      <c r="P754" t="inlineStr"/>
+      <c r="Q754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
@@ -40530,6 +40356,49 @@
       <c r="Q756" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B757" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C757" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D757" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E757" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F757" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G757" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H757" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I757" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J757" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K757" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L757" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M757" t="inlineStr"/>
+      <c r="N757" t="inlineStr"/>
+      <c r="O757" t="inlineStr"/>
+      <c r="P757" t="inlineStr"/>
+      <c r="Q757" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q757"/>
+  <dimension ref="A1:Q758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39385,21 +39385,11 @@
       <c r="L736" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M736" t="n">
-        <v>0</v>
-      </c>
-      <c r="N736" t="n">
-        <v>0</v>
-      </c>
-      <c r="O736" t="n">
-        <v>0</v>
-      </c>
-      <c r="P736" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q736" t="n">
-        <v>0</v>
-      </c>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" t="inlineStr"/>
+      <c r="O736" t="inlineStr"/>
+      <c r="P736" t="inlineStr"/>
+      <c r="Q736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
@@ -39534,21 +39524,11 @@
       <c r="L739" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M739" t="n">
-        <v>0</v>
-      </c>
-      <c r="N739" t="n">
-        <v>0</v>
-      </c>
-      <c r="O739" t="n">
-        <v>0</v>
-      </c>
-      <c r="P739" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q739" t="n">
-        <v>0</v>
-      </c>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr"/>
+      <c r="O739" t="inlineStr"/>
+      <c r="P739" t="inlineStr"/>
+      <c r="Q739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -39828,21 +39808,11 @@
       <c r="L745" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M745" t="n">
-        <v>0</v>
-      </c>
-      <c r="N745" t="n">
-        <v>0</v>
-      </c>
-      <c r="O745" t="n">
-        <v>0</v>
-      </c>
-      <c r="P745" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q745" t="n">
-        <v>0</v>
-      </c>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" t="inlineStr"/>
+      <c r="O745" t="inlineStr"/>
+      <c r="P745" t="inlineStr"/>
+      <c r="Q745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
@@ -40288,21 +40258,11 @@
       <c r="L755" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M755" t="n">
-        <v>0</v>
-      </c>
-      <c r="N755" t="n">
-        <v>0</v>
-      </c>
-      <c r="O755" t="n">
-        <v>0</v>
-      </c>
-      <c r="P755" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q755" t="n">
-        <v>0</v>
-      </c>
+      <c r="M755" t="inlineStr"/>
+      <c r="N755" t="inlineStr"/>
+      <c r="O755" t="inlineStr"/>
+      <c r="P755" t="inlineStr"/>
+      <c r="Q755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
@@ -40400,6 +40360,49 @@
       <c r="P757" t="inlineStr"/>
       <c r="Q757" t="inlineStr"/>
     </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B758" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C758" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D758" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E758" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F758" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G758" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H758" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I758" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J758" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K758" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L758" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M758" t="inlineStr"/>
+      <c r="N758" t="inlineStr"/>
+      <c r="O758" t="inlineStr"/>
+      <c r="P758" t="inlineStr"/>
+      <c r="Q758" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q758"/>
+  <dimension ref="A1:Q761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39428,21 +39428,11 @@
       <c r="L737" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M737" t="n">
-        <v>0</v>
-      </c>
-      <c r="N737" t="n">
-        <v>0</v>
-      </c>
-      <c r="O737" t="n">
-        <v>0</v>
-      </c>
-      <c r="P737" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q737" t="n">
-        <v>0</v>
-      </c>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" t="inlineStr"/>
+      <c r="O737" t="inlineStr"/>
+      <c r="P737" t="inlineStr"/>
+      <c r="Q737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
@@ -40403,6 +40393,135 @@
       <c r="P758" t="inlineStr"/>
       <c r="Q758" t="inlineStr"/>
     </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B759" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C759" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D759" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E759" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F759" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G759" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H759" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I759" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J759" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K759" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L759" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M759" t="inlineStr"/>
+      <c r="N759" t="inlineStr"/>
+      <c r="O759" t="inlineStr"/>
+      <c r="P759" t="inlineStr"/>
+      <c r="Q759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B760" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C760" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D760" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E760" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F760" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G760" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H760" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I760" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J760" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K760" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L760" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M760" t="inlineStr"/>
+      <c r="N760" t="inlineStr"/>
+      <c r="O760" t="inlineStr"/>
+      <c r="P760" t="inlineStr"/>
+      <c r="Q760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B761" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C761" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D761" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E761" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F761" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G761" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H761" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I761" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J761" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K761" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L761" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M761" t="inlineStr"/>
+      <c r="N761" t="inlineStr"/>
+      <c r="O761" t="inlineStr"/>
+      <c r="P761" t="inlineStr"/>
+      <c r="Q761" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q761"/>
+  <dimension ref="A1:Q763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39084,11 +39084,21 @@
       <c r="L729" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M729" t="inlineStr"/>
-      <c r="N729" t="inlineStr"/>
-      <c r="O729" t="inlineStr"/>
-      <c r="P729" t="inlineStr"/>
-      <c r="Q729" t="inlineStr"/>
+      <c r="M729" t="n">
+        <v>0</v>
+      </c>
+      <c r="N729" t="n">
+        <v>0</v>
+      </c>
+      <c r="O729" t="n">
+        <v>0</v>
+      </c>
+      <c r="P729" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q729" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
@@ -39127,11 +39137,21 @@
       <c r="L730" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M730" t="inlineStr"/>
-      <c r="N730" t="inlineStr"/>
-      <c r="O730" t="inlineStr"/>
-      <c r="P730" t="inlineStr"/>
-      <c r="Q730" t="inlineStr"/>
+      <c r="M730" t="n">
+        <v>0</v>
+      </c>
+      <c r="N730" t="n">
+        <v>0</v>
+      </c>
+      <c r="O730" t="n">
+        <v>0</v>
+      </c>
+      <c r="P730" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q730" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
@@ -39170,11 +39190,21 @@
       <c r="L731" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M731" t="inlineStr"/>
-      <c r="N731" t="inlineStr"/>
-      <c r="O731" t="inlineStr"/>
-      <c r="P731" t="inlineStr"/>
-      <c r="Q731" t="inlineStr"/>
+      <c r="M731" t="n">
+        <v>0</v>
+      </c>
+      <c r="N731" t="n">
+        <v>0</v>
+      </c>
+      <c r="O731" t="n">
+        <v>0</v>
+      </c>
+      <c r="P731" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q731" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
@@ -39213,11 +39243,21 @@
       <c r="L732" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M732" t="inlineStr"/>
-      <c r="N732" t="inlineStr"/>
-      <c r="O732" t="inlineStr"/>
-      <c r="P732" t="inlineStr"/>
-      <c r="Q732" t="inlineStr"/>
+      <c r="M732" t="n">
+        <v>0</v>
+      </c>
+      <c r="N732" t="n">
+        <v>0</v>
+      </c>
+      <c r="O732" t="n">
+        <v>0</v>
+      </c>
+      <c r="P732" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q732" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
@@ -39256,11 +39296,21 @@
       <c r="L733" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M733" t="inlineStr"/>
-      <c r="N733" t="inlineStr"/>
-      <c r="O733" t="inlineStr"/>
-      <c r="P733" t="inlineStr"/>
-      <c r="Q733" t="inlineStr"/>
+      <c r="M733" t="n">
+        <v>0</v>
+      </c>
+      <c r="N733" t="n">
+        <v>0</v>
+      </c>
+      <c r="O733" t="n">
+        <v>0</v>
+      </c>
+      <c r="P733" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q733" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
@@ -39299,11 +39349,21 @@
       <c r="L734" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M734" t="inlineStr"/>
-      <c r="N734" t="inlineStr"/>
-      <c r="O734" t="inlineStr"/>
-      <c r="P734" t="inlineStr"/>
-      <c r="Q734" t="inlineStr"/>
+      <c r="M734" t="n">
+        <v>0</v>
+      </c>
+      <c r="N734" t="n">
+        <v>0</v>
+      </c>
+      <c r="O734" t="n">
+        <v>0</v>
+      </c>
+      <c r="P734" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q734" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
@@ -39342,11 +39402,21 @@
       <c r="L735" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M735" t="inlineStr"/>
-      <c r="N735" t="inlineStr"/>
-      <c r="O735" t="inlineStr"/>
-      <c r="P735" t="inlineStr"/>
-      <c r="Q735" t="inlineStr"/>
+      <c r="M735" t="n">
+        <v>0</v>
+      </c>
+      <c r="N735" t="n">
+        <v>0</v>
+      </c>
+      <c r="O735" t="n">
+        <v>0</v>
+      </c>
+      <c r="P735" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q735" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
@@ -39385,11 +39455,21 @@
       <c r="L736" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M736" t="inlineStr"/>
-      <c r="N736" t="inlineStr"/>
-      <c r="O736" t="inlineStr"/>
-      <c r="P736" t="inlineStr"/>
-      <c r="Q736" t="inlineStr"/>
+      <c r="M736" t="n">
+        <v>0</v>
+      </c>
+      <c r="N736" t="n">
+        <v>0</v>
+      </c>
+      <c r="O736" t="n">
+        <v>0</v>
+      </c>
+      <c r="P736" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q736" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
@@ -39428,11 +39508,21 @@
       <c r="L737" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M737" t="inlineStr"/>
-      <c r="N737" t="inlineStr"/>
-      <c r="O737" t="inlineStr"/>
-      <c r="P737" t="inlineStr"/>
-      <c r="Q737" t="inlineStr"/>
+      <c r="M737" t="n">
+        <v>0</v>
+      </c>
+      <c r="N737" t="n">
+        <v>0</v>
+      </c>
+      <c r="O737" t="n">
+        <v>0</v>
+      </c>
+      <c r="P737" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q737" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
@@ -39471,11 +39561,21 @@
       <c r="L738" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M738" t="inlineStr"/>
-      <c r="N738" t="inlineStr"/>
-      <c r="O738" t="inlineStr"/>
-      <c r="P738" t="inlineStr"/>
-      <c r="Q738" t="inlineStr"/>
+      <c r="M738" t="n">
+        <v>0</v>
+      </c>
+      <c r="N738" t="n">
+        <v>0</v>
+      </c>
+      <c r="O738" t="n">
+        <v>0</v>
+      </c>
+      <c r="P738" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q738" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -39514,11 +39614,21 @@
       <c r="L739" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M739" t="inlineStr"/>
-      <c r="N739" t="inlineStr"/>
-      <c r="O739" t="inlineStr"/>
-      <c r="P739" t="inlineStr"/>
-      <c r="Q739" t="inlineStr"/>
+      <c r="M739" t="n">
+        <v>0</v>
+      </c>
+      <c r="N739" t="n">
+        <v>0</v>
+      </c>
+      <c r="O739" t="n">
+        <v>0</v>
+      </c>
+      <c r="P739" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q739" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -39710,15 +39820,27 @@
       <c r="J743" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="n">
+        <v>0</v>
+      </c>
       <c r="L743" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M743" t="inlineStr"/>
-      <c r="N743" t="inlineStr"/>
-      <c r="O743" t="inlineStr"/>
-      <c r="P743" t="inlineStr"/>
-      <c r="Q743" t="inlineStr"/>
+      <c r="M743" t="n">
+        <v>0</v>
+      </c>
+      <c r="N743" t="n">
+        <v>0</v>
+      </c>
+      <c r="O743" t="n">
+        <v>0</v>
+      </c>
+      <c r="P743" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q743" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
@@ -39751,15 +39873,27 @@
       <c r="J744" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="n">
+        <v>0</v>
+      </c>
       <c r="L744" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M744" t="inlineStr"/>
-      <c r="N744" t="inlineStr"/>
-      <c r="O744" t="inlineStr"/>
-      <c r="P744" t="inlineStr"/>
-      <c r="Q744" t="inlineStr"/>
+      <c r="M744" t="n">
+        <v>0</v>
+      </c>
+      <c r="N744" t="n">
+        <v>0</v>
+      </c>
+      <c r="O744" t="n">
+        <v>0</v>
+      </c>
+      <c r="P744" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q744" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
@@ -39798,11 +39932,21 @@
       <c r="L745" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M745" t="inlineStr"/>
-      <c r="N745" t="inlineStr"/>
-      <c r="O745" t="inlineStr"/>
-      <c r="P745" t="inlineStr"/>
-      <c r="Q745" t="inlineStr"/>
+      <c r="M745" t="n">
+        <v>0</v>
+      </c>
+      <c r="N745" t="n">
+        <v>0</v>
+      </c>
+      <c r="O745" t="n">
+        <v>0</v>
+      </c>
+      <c r="P745" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q745" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
@@ -39947,11 +40091,21 @@
       <c r="L748" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M748" t="inlineStr"/>
-      <c r="N748" t="inlineStr"/>
-      <c r="O748" t="inlineStr"/>
-      <c r="P748" t="inlineStr"/>
-      <c r="Q748" t="inlineStr"/>
+      <c r="M748" t="n">
+        <v>0</v>
+      </c>
+      <c r="N748" t="n">
+        <v>0</v>
+      </c>
+      <c r="O748" t="n">
+        <v>0</v>
+      </c>
+      <c r="P748" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q748" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
@@ -39990,11 +40144,21 @@
       <c r="L749" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M749" t="inlineStr"/>
-      <c r="N749" t="inlineStr"/>
-      <c r="O749" t="inlineStr"/>
-      <c r="P749" t="inlineStr"/>
-      <c r="Q749" t="inlineStr"/>
+      <c r="M749" t="n">
+        <v>0</v>
+      </c>
+      <c r="N749" t="n">
+        <v>0</v>
+      </c>
+      <c r="O749" t="n">
+        <v>0</v>
+      </c>
+      <c r="P749" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q749" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
@@ -40033,11 +40197,21 @@
       <c r="L750" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M750" t="inlineStr"/>
-      <c r="N750" t="inlineStr"/>
-      <c r="O750" t="inlineStr"/>
-      <c r="P750" t="inlineStr"/>
-      <c r="Q750" t="inlineStr"/>
+      <c r="M750" t="n">
+        <v>0</v>
+      </c>
+      <c r="N750" t="n">
+        <v>0</v>
+      </c>
+      <c r="O750" t="n">
+        <v>0</v>
+      </c>
+      <c r="P750" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q750" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
@@ -40076,11 +40250,21 @@
       <c r="L751" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M751" t="inlineStr"/>
-      <c r="N751" t="inlineStr"/>
-      <c r="O751" t="inlineStr"/>
-      <c r="P751" t="inlineStr"/>
-      <c r="Q751" t="inlineStr"/>
+      <c r="M751" t="n">
+        <v>0</v>
+      </c>
+      <c r="N751" t="n">
+        <v>0</v>
+      </c>
+      <c r="O751" t="n">
+        <v>0</v>
+      </c>
+      <c r="P751" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q751" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
@@ -40119,11 +40303,21 @@
       <c r="L752" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M752" t="inlineStr"/>
-      <c r="N752" t="inlineStr"/>
-      <c r="O752" t="inlineStr"/>
-      <c r="P752" t="inlineStr"/>
-      <c r="Q752" t="inlineStr"/>
+      <c r="M752" t="n">
+        <v>0</v>
+      </c>
+      <c r="N752" t="n">
+        <v>0</v>
+      </c>
+      <c r="O752" t="n">
+        <v>0</v>
+      </c>
+      <c r="P752" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q752" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
@@ -40162,11 +40356,21 @@
       <c r="L753" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M753" t="inlineStr"/>
-      <c r="N753" t="inlineStr"/>
-      <c r="O753" t="inlineStr"/>
-      <c r="P753" t="inlineStr"/>
-      <c r="Q753" t="inlineStr"/>
+      <c r="M753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N753" t="n">
+        <v>0</v>
+      </c>
+      <c r="O753" t="n">
+        <v>0</v>
+      </c>
+      <c r="P753" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q753" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
@@ -40205,11 +40409,21 @@
       <c r="L754" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M754" t="inlineStr"/>
-      <c r="N754" t="inlineStr"/>
-      <c r="O754" t="inlineStr"/>
-      <c r="P754" t="inlineStr"/>
-      <c r="Q754" t="inlineStr"/>
+      <c r="M754" t="n">
+        <v>0</v>
+      </c>
+      <c r="N754" t="n">
+        <v>0</v>
+      </c>
+      <c r="O754" t="n">
+        <v>0</v>
+      </c>
+      <c r="P754" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q754" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
@@ -40248,11 +40462,21 @@
       <c r="L755" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M755" t="inlineStr"/>
-      <c r="N755" t="inlineStr"/>
-      <c r="O755" t="inlineStr"/>
-      <c r="P755" t="inlineStr"/>
-      <c r="Q755" t="inlineStr"/>
+      <c r="M755" t="n">
+        <v>0</v>
+      </c>
+      <c r="N755" t="n">
+        <v>0</v>
+      </c>
+      <c r="O755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P755" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q755" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
@@ -40344,11 +40568,21 @@
       <c r="L757" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M757" t="inlineStr"/>
-      <c r="N757" t="inlineStr"/>
-      <c r="O757" t="inlineStr"/>
-      <c r="P757" t="inlineStr"/>
-      <c r="Q757" t="inlineStr"/>
+      <c r="M757" t="n">
+        <v>0</v>
+      </c>
+      <c r="N757" t="n">
+        <v>0</v>
+      </c>
+      <c r="O757" t="n">
+        <v>0</v>
+      </c>
+      <c r="P757" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q757" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
@@ -40387,11 +40621,21 @@
       <c r="L758" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M758" t="inlineStr"/>
-      <c r="N758" t="inlineStr"/>
-      <c r="O758" t="inlineStr"/>
-      <c r="P758" t="inlineStr"/>
-      <c r="Q758" t="inlineStr"/>
+      <c r="M758" t="n">
+        <v>0</v>
+      </c>
+      <c r="N758" t="n">
+        <v>0</v>
+      </c>
+      <c r="O758" t="n">
+        <v>0</v>
+      </c>
+      <c r="P758" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q758" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
@@ -40430,11 +40674,21 @@
       <c r="L759" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M759" t="inlineStr"/>
-      <c r="N759" t="inlineStr"/>
-      <c r="O759" t="inlineStr"/>
-      <c r="P759" t="inlineStr"/>
-      <c r="Q759" t="inlineStr"/>
+      <c r="M759" t="n">
+        <v>0</v>
+      </c>
+      <c r="N759" t="n">
+        <v>0</v>
+      </c>
+      <c r="O759" t="n">
+        <v>0</v>
+      </c>
+      <c r="P759" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q759" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
@@ -40473,11 +40727,21 @@
       <c r="L760" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M760" t="inlineStr"/>
-      <c r="N760" t="inlineStr"/>
-      <c r="O760" t="inlineStr"/>
-      <c r="P760" t="inlineStr"/>
-      <c r="Q760" t="inlineStr"/>
+      <c r="M760" t="n">
+        <v>0</v>
+      </c>
+      <c r="N760" t="n">
+        <v>0</v>
+      </c>
+      <c r="O760" t="n">
+        <v>0</v>
+      </c>
+      <c r="P760" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q760" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
@@ -40516,11 +40780,127 @@
       <c r="L761" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M761" t="inlineStr"/>
-      <c r="N761" t="inlineStr"/>
-      <c r="O761" t="inlineStr"/>
-      <c r="P761" t="inlineStr"/>
-      <c r="Q761" t="inlineStr"/>
+      <c r="M761" t="n">
+        <v>0</v>
+      </c>
+      <c r="N761" t="n">
+        <v>0</v>
+      </c>
+      <c r="O761" t="n">
+        <v>0</v>
+      </c>
+      <c r="P761" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q761" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B762" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C762" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D762" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E762" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F762" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G762" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H762" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I762" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J762" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K762" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L762" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M762" t="n">
+        <v>0</v>
+      </c>
+      <c r="N762" t="n">
+        <v>0</v>
+      </c>
+      <c r="O762" t="n">
+        <v>0</v>
+      </c>
+      <c r="P762" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q762" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B763" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C763" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D763" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E763" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F763" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G763" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H763" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I763" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J763" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K763" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L763" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M763" t="n">
+        <v>0</v>
+      </c>
+      <c r="N763" t="n">
+        <v>0</v>
+      </c>
+      <c r="O763" t="n">
+        <v>0</v>
+      </c>
+      <c r="P763" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q763" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q763"/>
+  <dimension ref="A1:Q765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39508,21 +39508,11 @@
       <c r="L737" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M737" t="n">
-        <v>0</v>
-      </c>
-      <c r="N737" t="n">
-        <v>0</v>
-      </c>
-      <c r="O737" t="n">
-        <v>0</v>
-      </c>
-      <c r="P737" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q737" t="n">
-        <v>0</v>
-      </c>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" t="inlineStr"/>
+      <c r="O737" t="inlineStr"/>
+      <c r="P737" t="inlineStr"/>
+      <c r="Q737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
@@ -39561,21 +39551,11 @@
       <c r="L738" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M738" t="n">
-        <v>0</v>
-      </c>
-      <c r="N738" t="n">
-        <v>0</v>
-      </c>
-      <c r="O738" t="n">
-        <v>0</v>
-      </c>
-      <c r="P738" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q738" t="n">
-        <v>0</v>
-      </c>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr"/>
+      <c r="O738" t="inlineStr"/>
+      <c r="P738" t="inlineStr"/>
+      <c r="Q738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -39614,21 +39594,11 @@
       <c r="L739" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M739" t="n">
-        <v>0</v>
-      </c>
-      <c r="N739" t="n">
-        <v>0</v>
-      </c>
-      <c r="O739" t="n">
-        <v>0</v>
-      </c>
-      <c r="P739" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q739" t="n">
-        <v>0</v>
-      </c>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr"/>
+      <c r="O739" t="inlineStr"/>
+      <c r="P739" t="inlineStr"/>
+      <c r="Q739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -39667,21 +39637,11 @@
       <c r="L740" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M740" t="n">
-        <v>0</v>
-      </c>
-      <c r="N740" t="n">
-        <v>0</v>
-      </c>
-      <c r="O740" t="n">
-        <v>0</v>
-      </c>
-      <c r="P740" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q740" t="n">
-        <v>0</v>
-      </c>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr"/>
+      <c r="O740" t="inlineStr"/>
+      <c r="P740" t="inlineStr"/>
+      <c r="Q740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
@@ -39720,21 +39680,11 @@
       <c r="L741" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M741" t="n">
-        <v>0</v>
-      </c>
-      <c r="N741" t="n">
-        <v>0</v>
-      </c>
-      <c r="O741" t="n">
-        <v>0</v>
-      </c>
-      <c r="P741" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q741" t="n">
-        <v>0</v>
-      </c>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr"/>
+      <c r="O741" t="inlineStr"/>
+      <c r="P741" t="inlineStr"/>
+      <c r="Q741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
@@ -39767,27 +39717,15 @@
       <c r="J742" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K742" t="n">
-        <v>0</v>
-      </c>
+      <c r="K742" t="inlineStr"/>
       <c r="L742" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M742" t="n">
-        <v>0</v>
-      </c>
-      <c r="N742" t="n">
-        <v>0</v>
-      </c>
-      <c r="O742" t="n">
-        <v>0</v>
-      </c>
-      <c r="P742" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q742" t="n">
-        <v>0</v>
-      </c>
+      <c r="M742" t="inlineStr"/>
+      <c r="N742" t="inlineStr"/>
+      <c r="O742" t="inlineStr"/>
+      <c r="P742" t="inlineStr"/>
+      <c r="Q742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
@@ -40409,21 +40347,11 @@
       <c r="L754" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M754" t="n">
-        <v>0</v>
-      </c>
-      <c r="N754" t="n">
-        <v>0</v>
-      </c>
-      <c r="O754" t="n">
-        <v>0</v>
-      </c>
-      <c r="P754" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q754" t="n">
-        <v>0</v>
-      </c>
+      <c r="M754" t="inlineStr"/>
+      <c r="N754" t="inlineStr"/>
+      <c r="O754" t="inlineStr"/>
+      <c r="P754" t="inlineStr"/>
+      <c r="Q754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
@@ -40462,21 +40390,11 @@
       <c r="L755" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M755" t="n">
-        <v>0</v>
-      </c>
-      <c r="N755" t="n">
-        <v>0</v>
-      </c>
-      <c r="O755" t="n">
-        <v>0</v>
-      </c>
-      <c r="P755" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q755" t="n">
-        <v>0</v>
-      </c>
+      <c r="M755" t="inlineStr"/>
+      <c r="N755" t="inlineStr"/>
+      <c r="O755" t="inlineStr"/>
+      <c r="P755" t="inlineStr"/>
+      <c r="Q755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
@@ -40515,21 +40433,11 @@
       <c r="L756" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M756" t="n">
-        <v>0</v>
-      </c>
-      <c r="N756" t="n">
-        <v>0</v>
-      </c>
-      <c r="O756" t="n">
-        <v>0</v>
-      </c>
-      <c r="P756" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q756" t="n">
-        <v>0</v>
-      </c>
+      <c r="M756" t="inlineStr"/>
+      <c r="N756" t="inlineStr"/>
+      <c r="O756" t="inlineStr"/>
+      <c r="P756" t="inlineStr"/>
+      <c r="Q756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
@@ -40568,21 +40476,11 @@
       <c r="L757" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M757" t="n">
-        <v>0</v>
-      </c>
-      <c r="N757" t="n">
-        <v>0</v>
-      </c>
-      <c r="O757" t="n">
-        <v>0</v>
-      </c>
-      <c r="P757" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q757" t="n">
-        <v>0</v>
-      </c>
+      <c r="M757" t="inlineStr"/>
+      <c r="N757" t="inlineStr"/>
+      <c r="O757" t="inlineStr"/>
+      <c r="P757" t="inlineStr"/>
+      <c r="Q757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
@@ -40621,21 +40519,11 @@
       <c r="L758" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M758" t="n">
-        <v>0</v>
-      </c>
-      <c r="N758" t="n">
-        <v>0</v>
-      </c>
-      <c r="O758" t="n">
-        <v>0</v>
-      </c>
-      <c r="P758" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q758" t="n">
-        <v>0</v>
-      </c>
+      <c r="M758" t="inlineStr"/>
+      <c r="N758" t="inlineStr"/>
+      <c r="O758" t="inlineStr"/>
+      <c r="P758" t="inlineStr"/>
+      <c r="Q758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
@@ -40674,21 +40562,11 @@
       <c r="L759" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M759" t="n">
-        <v>0</v>
-      </c>
-      <c r="N759" t="n">
-        <v>0</v>
-      </c>
-      <c r="O759" t="n">
-        <v>0</v>
-      </c>
-      <c r="P759" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q759" t="n">
-        <v>0</v>
-      </c>
+      <c r="M759" t="inlineStr"/>
+      <c r="N759" t="inlineStr"/>
+      <c r="O759" t="inlineStr"/>
+      <c r="P759" t="inlineStr"/>
+      <c r="Q759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
@@ -40780,21 +40658,11 @@
       <c r="L761" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M761" t="n">
-        <v>0</v>
-      </c>
-      <c r="N761" t="n">
-        <v>0</v>
-      </c>
-      <c r="O761" t="n">
-        <v>0</v>
-      </c>
-      <c r="P761" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q761" t="n">
-        <v>0</v>
-      </c>
+      <c r="M761" t="inlineStr"/>
+      <c r="N761" t="inlineStr"/>
+      <c r="O761" t="inlineStr"/>
+      <c r="P761" t="inlineStr"/>
+      <c r="Q761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
@@ -40901,6 +40769,92 @@
       <c r="Q763" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B764" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C764" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D764" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E764" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F764" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G764" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H764" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I764" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J764" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K764" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L764" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M764" t="inlineStr"/>
+      <c r="N764" t="inlineStr"/>
+      <c r="O764" t="inlineStr"/>
+      <c r="P764" t="inlineStr"/>
+      <c r="Q764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B765" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C765" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D765" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E765" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F765" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G765" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H765" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I765" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J765" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K765" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L765" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M765" t="inlineStr"/>
+      <c r="N765" t="inlineStr"/>
+      <c r="O765" t="inlineStr"/>
+      <c r="P765" t="inlineStr"/>
+      <c r="Q765" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q765"/>
+  <dimension ref="A1:Q766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39758,27 +39758,15 @@
       <c r="J743" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K743" t="n">
-        <v>0</v>
-      </c>
+      <c r="K743" t="inlineStr"/>
       <c r="L743" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M743" t="n">
-        <v>0</v>
-      </c>
-      <c r="N743" t="n">
-        <v>0</v>
-      </c>
-      <c r="O743" t="n">
-        <v>0</v>
-      </c>
-      <c r="P743" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q743" t="n">
-        <v>0</v>
-      </c>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" t="inlineStr"/>
+      <c r="O743" t="inlineStr"/>
+      <c r="P743" t="inlineStr"/>
+      <c r="Q743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
@@ -39811,27 +39799,15 @@
       <c r="J744" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K744" t="n">
-        <v>0</v>
-      </c>
+      <c r="K744" t="inlineStr"/>
       <c r="L744" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M744" t="n">
-        <v>0</v>
-      </c>
-      <c r="N744" t="n">
-        <v>0</v>
-      </c>
-      <c r="O744" t="n">
-        <v>0</v>
-      </c>
-      <c r="P744" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q744" t="n">
-        <v>0</v>
-      </c>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" t="inlineStr"/>
+      <c r="O744" t="inlineStr"/>
+      <c r="P744" t="inlineStr"/>
+      <c r="Q744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
@@ -39976,21 +39952,11 @@
       <c r="L747" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M747" t="n">
-        <v>0</v>
-      </c>
-      <c r="N747" t="n">
-        <v>0</v>
-      </c>
-      <c r="O747" t="n">
-        <v>0</v>
-      </c>
-      <c r="P747" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q747" t="n">
-        <v>0</v>
-      </c>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" t="inlineStr"/>
+      <c r="O747" t="inlineStr"/>
+      <c r="P747" t="inlineStr"/>
+      <c r="Q747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
@@ -40241,21 +40207,11 @@
       <c r="L752" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M752" t="n">
-        <v>0</v>
-      </c>
-      <c r="N752" t="n">
-        <v>0</v>
-      </c>
-      <c r="O752" t="n">
-        <v>0</v>
-      </c>
-      <c r="P752" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q752" t="n">
-        <v>0</v>
-      </c>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr"/>
+      <c r="O752" t="inlineStr"/>
+      <c r="P752" t="inlineStr"/>
+      <c r="Q752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
@@ -40294,21 +40250,11 @@
       <c r="L753" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M753" t="n">
-        <v>0</v>
-      </c>
-      <c r="N753" t="n">
-        <v>0</v>
-      </c>
-      <c r="O753" t="n">
-        <v>0</v>
-      </c>
-      <c r="P753" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q753" t="n">
-        <v>0</v>
-      </c>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr"/>
+      <c r="O753" t="inlineStr"/>
+      <c r="P753" t="inlineStr"/>
+      <c r="Q753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
@@ -40605,21 +40551,11 @@
       <c r="L760" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M760" t="n">
-        <v>0</v>
-      </c>
-      <c r="N760" t="n">
-        <v>0</v>
-      </c>
-      <c r="O760" t="n">
-        <v>0</v>
-      </c>
-      <c r="P760" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q760" t="n">
-        <v>0</v>
-      </c>
+      <c r="M760" t="inlineStr"/>
+      <c r="N760" t="inlineStr"/>
+      <c r="O760" t="inlineStr"/>
+      <c r="P760" t="inlineStr"/>
+      <c r="Q760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
@@ -40701,21 +40637,11 @@
       <c r="L762" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M762" t="n">
-        <v>0</v>
-      </c>
-      <c r="N762" t="n">
-        <v>0</v>
-      </c>
-      <c r="O762" t="n">
-        <v>0</v>
-      </c>
-      <c r="P762" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q762" t="n">
-        <v>0</v>
-      </c>
+      <c r="M762" t="inlineStr"/>
+      <c r="N762" t="inlineStr"/>
+      <c r="O762" t="inlineStr"/>
+      <c r="P762" t="inlineStr"/>
+      <c r="Q762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
@@ -40754,21 +40680,11 @@
       <c r="L763" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M763" t="n">
-        <v>0</v>
-      </c>
-      <c r="N763" t="n">
-        <v>0</v>
-      </c>
-      <c r="O763" t="n">
-        <v>0</v>
-      </c>
-      <c r="P763" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q763" t="n">
-        <v>0</v>
-      </c>
+      <c r="M763" t="inlineStr"/>
+      <c r="N763" t="inlineStr"/>
+      <c r="O763" t="inlineStr"/>
+      <c r="P763" t="inlineStr"/>
+      <c r="Q763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
@@ -40856,6 +40772,49 @@
       <c r="P765" t="inlineStr"/>
       <c r="Q765" t="inlineStr"/>
     </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B766" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C766" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D766" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E766" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F766" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G766" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H766" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I766" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J766" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K766" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L766" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M766" t="inlineStr"/>
+      <c r="N766" t="inlineStr"/>
+      <c r="O766" t="inlineStr"/>
+      <c r="P766" t="inlineStr"/>
+      <c r="Q766" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Quantities.xlsx
+++ b/BinancePTF/Quantities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q766"/>
+  <dimension ref="A1:Q767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39508,11 +39508,21 @@
       <c r="L737" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M737" t="inlineStr"/>
-      <c r="N737" t="inlineStr"/>
-      <c r="O737" t="inlineStr"/>
-      <c r="P737" t="inlineStr"/>
-      <c r="Q737" t="inlineStr"/>
+      <c r="M737" t="n">
+        <v>0</v>
+      </c>
+      <c r="N737" t="n">
+        <v>0</v>
+      </c>
+      <c r="O737" t="n">
+        <v>0</v>
+      </c>
+      <c r="P737" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q737" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
@@ -39551,11 +39561,21 @@
       <c r="L738" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M738" t="inlineStr"/>
-      <c r="N738" t="inlineStr"/>
-      <c r="O738" t="inlineStr"/>
-      <c r="P738" t="inlineStr"/>
-      <c r="Q738" t="inlineStr"/>
+      <c r="M738" t="n">
+        <v>0</v>
+      </c>
+      <c r="N738" t="n">
+        <v>0</v>
+      </c>
+      <c r="O738" t="n">
+        <v>0</v>
+      </c>
+      <c r="P738" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q738" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -39594,11 +39614,21 @@
       <c r="L739" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M739" t="inlineStr"/>
-      <c r="N739" t="inlineStr"/>
-      <c r="O739" t="inlineStr"/>
-      <c r="P739" t="inlineStr"/>
-      <c r="Q739" t="inlineStr"/>
+      <c r="M739" t="n">
+        <v>0</v>
+      </c>
+      <c r="N739" t="n">
+        <v>0</v>
+      </c>
+      <c r="O739" t="n">
+        <v>0</v>
+      </c>
+      <c r="P739" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q739" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -39637,11 +39667,21 @@
       <c r="L740" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M740" t="inlineStr"/>
-      <c r="N740" t="inlineStr"/>
-      <c r="O740" t="inlineStr"/>
-      <c r="P740" t="inlineStr"/>
-      <c r="Q740" t="inlineStr"/>
+      <c r="M740" t="n">
+        <v>0</v>
+      </c>
+      <c r="N740" t="n">
+        <v>0</v>
+      </c>
+      <c r="O740" t="n">
+        <v>0</v>
+      </c>
+      <c r="P740" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q740" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
@@ -39680,11 +39720,21 @@
       <c r="L741" t="n">
         <v>0.14694965</v>
       </c>
-      <c r="M741" t="inlineStr"/>
-      <c r="N741" t="inlineStr"/>
-      <c r="O741" t="inlineStr"/>
-      <c r="P741" t="inlineStr"/>
-      <c r="Q741" t="inlineStr"/>
+      <c r="M741" t="n">
+        <v>0</v>
+      </c>
+      <c r="N741" t="n">
+        <v>0</v>
+      </c>
+      <c r="O741" t="n">
+        <v>0</v>
+      </c>
+      <c r="P741" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q741" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
@@ -39717,15 +39767,27 @@
       <c r="J742" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="n">
+        <v>0</v>
+      </c>
       <c r="L742" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M742" t="inlineStr"/>
-      <c r="N742" t="inlineStr"/>
-      <c r="O742" t="inlineStr"/>
-      <c r="P742" t="inlineStr"/>
-      <c r="Q742" t="inlineStr"/>
+      <c r="M742" t="n">
+        <v>0</v>
+      </c>
+      <c r="N742" t="n">
+        <v>0</v>
+      </c>
+      <c r="O742" t="n">
+        <v>0</v>
+      </c>
+      <c r="P742" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q742" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
@@ -39758,15 +39820,27 @@
       <c r="J743" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="n">
+        <v>0</v>
+      </c>
       <c r="L743" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M743" t="inlineStr"/>
-      <c r="N743" t="inlineStr"/>
-      <c r="O743" t="inlineStr"/>
-      <c r="P743" t="inlineStr"/>
-      <c r="Q743" t="inlineStr"/>
+      <c r="M743" t="n">
+        <v>0</v>
+      </c>
+      <c r="N743" t="n">
+        <v>0</v>
+      </c>
+      <c r="O743" t="n">
+        <v>0</v>
+      </c>
+      <c r="P743" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q743" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
@@ -39799,15 +39873,27 @@
       <c r="J744" t="n">
         <v>4663.85449423</v>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="n">
+        <v>0</v>
+      </c>
       <c r="L744" t="n">
         <v>0.02794965</v>
       </c>
-      <c r="M744" t="inlineStr"/>
-      <c r="N744" t="inlineStr"/>
-      <c r="O744" t="inlineStr"/>
-      <c r="P744" t="inlineStr"/>
-      <c r="Q744" t="inlineStr"/>
+      <c r="M744" t="n">
+        <v>0</v>
+      </c>
+      <c r="N744" t="n">
+        <v>0</v>
+      </c>
+      <c r="O744" t="n">
+        <v>0</v>
+      </c>
+      <c r="P744" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q744" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
@@ -39952,11 +40038,21 @@
       <c r="L747" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M747" t="inlineStr"/>
-      <c r="N747" t="inlineStr"/>
-      <c r="O747" t="inlineStr"/>
-      <c r="P747" t="inlineStr"/>
-      <c r="Q747" t="inlineStr"/>
+      <c r="M747" t="n">
+        <v>0</v>
+      </c>
+      <c r="N747" t="n">
+        <v>0</v>
+      </c>
+      <c r="O747" t="n">
+        <v>0</v>
+      </c>
+      <c r="P747" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q747" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
@@ -40207,11 +40303,21 @@
       <c r="L752" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M752" t="inlineStr"/>
-      <c r="N752" t="inlineStr"/>
-      <c r="O752" t="inlineStr"/>
-      <c r="P752" t="inlineStr"/>
-      <c r="Q752" t="inlineStr"/>
+      <c r="M752" t="n">
+        <v>0</v>
+      </c>
+      <c r="N752" t="n">
+        <v>0</v>
+      </c>
+      <c r="O752" t="n">
+        <v>0</v>
+      </c>
+      <c r="P752" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q752" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
@@ -40250,11 +40356,21 @@
       <c r="L753" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M753" t="inlineStr"/>
-      <c r="N753" t="inlineStr"/>
-      <c r="O753" t="inlineStr"/>
-      <c r="P753" t="inlineStr"/>
-      <c r="Q753" t="inlineStr"/>
+      <c r="M753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N753" t="n">
+        <v>0</v>
+      </c>
+      <c r="O753" t="n">
+        <v>0</v>
+      </c>
+      <c r="P753" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q753" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
@@ -40293,11 +40409,21 @@
       <c r="L754" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M754" t="inlineStr"/>
-      <c r="N754" t="inlineStr"/>
-      <c r="O754" t="inlineStr"/>
-      <c r="P754" t="inlineStr"/>
-      <c r="Q754" t="inlineStr"/>
+      <c r="M754" t="n">
+        <v>0</v>
+      </c>
+      <c r="N754" t="n">
+        <v>0</v>
+      </c>
+      <c r="O754" t="n">
+        <v>0</v>
+      </c>
+      <c r="P754" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q754" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
@@ -40336,11 +40462,21 @@
       <c r="L755" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M755" t="inlineStr"/>
-      <c r="N755" t="inlineStr"/>
-      <c r="O755" t="inlineStr"/>
-      <c r="P755" t="inlineStr"/>
-      <c r="Q755" t="inlineStr"/>
+      <c r="M755" t="n">
+        <v>0</v>
+      </c>
+      <c r="N755" t="n">
+        <v>0</v>
+      </c>
+      <c r="O755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P755" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q755" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
@@ -40379,11 +40515,21 @@
       <c r="L756" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M756" t="inlineStr"/>
-      <c r="N756" t="inlineStr"/>
-      <c r="O756" t="inlineStr"/>
-      <c r="P756" t="inlineStr"/>
-      <c r="Q756" t="inlineStr"/>
+      <c r="M756" t="n">
+        <v>0</v>
+      </c>
+      <c r="N756" t="n">
+        <v>0</v>
+      </c>
+      <c r="O756" t="n">
+        <v>0</v>
+      </c>
+      <c r="P756" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q756" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
@@ -40422,11 +40568,21 @@
       <c r="L757" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M757" t="inlineStr"/>
-      <c r="N757" t="inlineStr"/>
-      <c r="O757" t="inlineStr"/>
-      <c r="P757" t="inlineStr"/>
-      <c r="Q757" t="inlineStr"/>
+      <c r="M757" t="n">
+        <v>0</v>
+      </c>
+      <c r="N757" t="n">
+        <v>0</v>
+      </c>
+      <c r="O757" t="n">
+        <v>0</v>
+      </c>
+      <c r="P757" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q757" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
@@ -40465,11 +40621,21 @@
       <c r="L758" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M758" t="inlineStr"/>
-      <c r="N758" t="inlineStr"/>
-      <c r="O758" t="inlineStr"/>
-      <c r="P758" t="inlineStr"/>
-      <c r="Q758" t="inlineStr"/>
+      <c r="M758" t="n">
+        <v>0</v>
+      </c>
+      <c r="N758" t="n">
+        <v>0</v>
+      </c>
+      <c r="O758" t="n">
+        <v>0</v>
+      </c>
+      <c r="P758" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q758" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
@@ -40508,11 +40674,21 @@
       <c r="L759" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M759" t="inlineStr"/>
-      <c r="N759" t="inlineStr"/>
-      <c r="O759" t="inlineStr"/>
-      <c r="P759" t="inlineStr"/>
-      <c r="Q759" t="inlineStr"/>
+      <c r="M759" t="n">
+        <v>0</v>
+      </c>
+      <c r="N759" t="n">
+        <v>0</v>
+      </c>
+      <c r="O759" t="n">
+        <v>0</v>
+      </c>
+      <c r="P759" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q759" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
@@ -40551,11 +40727,21 @@
       <c r="L760" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M760" t="inlineStr"/>
-      <c r="N760" t="inlineStr"/>
-      <c r="O760" t="inlineStr"/>
-      <c r="P760" t="inlineStr"/>
-      <c r="Q760" t="inlineStr"/>
+      <c r="M760" t="n">
+        <v>0</v>
+      </c>
+      <c r="N760" t="n">
+        <v>0</v>
+      </c>
+      <c r="O760" t="n">
+        <v>0</v>
+      </c>
+      <c r="P760" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q760" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
@@ -40594,11 +40780,21 @@
       <c r="L761" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M761" t="inlineStr"/>
-      <c r="N761" t="inlineStr"/>
-      <c r="O761" t="inlineStr"/>
-      <c r="P761" t="inlineStr"/>
-      <c r="Q761" t="inlineStr"/>
+      <c r="M761" t="n">
+        <v>0</v>
+      </c>
+      <c r="N761" t="n">
+        <v>0</v>
+      </c>
+      <c r="O761" t="n">
+        <v>0</v>
+      </c>
+      <c r="P761" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q761" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
@@ -40637,11 +40833,21 @@
       <c r="L762" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M762" t="inlineStr"/>
-      <c r="N762" t="inlineStr"/>
-      <c r="O762" t="inlineStr"/>
-      <c r="P762" t="inlineStr"/>
-      <c r="Q762" t="inlineStr"/>
+      <c r="M762" t="n">
+        <v>0</v>
+      </c>
+      <c r="N762" t="n">
+        <v>0</v>
+      </c>
+      <c r="O762" t="n">
+        <v>0</v>
+      </c>
+      <c r="P762" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q762" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
@@ -40680,11 +40886,21 @@
       <c r="L763" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M763" t="inlineStr"/>
-      <c r="N763" t="inlineStr"/>
-      <c r="O763" t="inlineStr"/>
-      <c r="P763" t="inlineStr"/>
-      <c r="Q763" t="inlineStr"/>
+      <c r="M763" t="n">
+        <v>0</v>
+      </c>
+      <c r="N763" t="n">
+        <v>0</v>
+      </c>
+      <c r="O763" t="n">
+        <v>0</v>
+      </c>
+      <c r="P763" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q763" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
@@ -40723,11 +40939,21 @@
       <c r="L764" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M764" t="inlineStr"/>
-      <c r="N764" t="inlineStr"/>
-      <c r="O764" t="inlineStr"/>
-      <c r="P764" t="inlineStr"/>
-      <c r="Q764" t="inlineStr"/>
+      <c r="M764" t="n">
+        <v>0</v>
+      </c>
+      <c r="N764" t="n">
+        <v>0</v>
+      </c>
+      <c r="O764" t="n">
+        <v>0</v>
+      </c>
+      <c r="P764" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q764" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
@@ -40766,11 +40992,21 @@
       <c r="L765" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M765" t="inlineStr"/>
-      <c r="N765" t="inlineStr"/>
-      <c r="O765" t="inlineStr"/>
-      <c r="P765" t="inlineStr"/>
-      <c r="Q765" t="inlineStr"/>
+      <c r="M765" t="n">
+        <v>0</v>
+      </c>
+      <c r="N765" t="n">
+        <v>0</v>
+      </c>
+      <c r="O765" t="n">
+        <v>0</v>
+      </c>
+      <c r="P765" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q765" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
@@ -40809,11 +41045,74 @@
       <c r="L766" t="n">
         <v>0.04994965</v>
       </c>
-      <c r="M766" t="inlineStr"/>
-      <c r="N766" t="inlineStr"/>
-      <c r="O766" t="inlineStr"/>
-      <c r="P766" t="inlineStr"/>
-      <c r="Q766" t="inlineStr"/>
+      <c r="M766" t="n">
+        <v>0</v>
+      </c>
+      <c r="N766" t="n">
+        <v>0</v>
+      </c>
+      <c r="O766" t="n">
+        <v>0</v>
+      </c>
+      <c r="P766" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q766" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B767" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C767" t="n">
+        <v>0.00084317</v>
+      </c>
+      <c r="D767" t="n">
+        <v>0.00148604</v>
+      </c>
+      <c r="E767" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F767" t="n">
+        <v>0.00027515</v>
+      </c>
+      <c r="G767" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H767" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I767" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J767" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K767" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="L767" t="n">
+        <v>0.04994965</v>
+      </c>
+      <c r="M767" t="n">
+        <v>0</v>
+      </c>
+      <c r="N767" t="n">
+        <v>0</v>
+      </c>
+      <c r="O767" t="n">
+        <v>0</v>
+      </c>
+      <c r="P767" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q767" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
